--- a/artfynd/A 15049-2024 artfynd.xlsx
+++ b/artfynd/A 15049-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>372674</v>
+        <v>116705109</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V Rödingsjön, Ås lm</t>
+          <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536099.9655042114</v>
+        <v>536070</v>
       </c>
       <c r="R2" t="n">
-        <v>7193662.449111543</v>
+        <v>7193799</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>372676</v>
+        <v>116705115</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V Rödingsjön, Ås lm</t>
+          <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535996.5126286015</v>
+        <v>536038</v>
       </c>
       <c r="R3" t="n">
-        <v>7193625.908300751</v>
+        <v>7193739</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,58 +873,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116705169</v>
+        <v>116705069</v>
       </c>
       <c r="B4" t="n">
-        <v>79556</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536034</v>
+        <v>536079</v>
       </c>
       <c r="R4" t="n">
-        <v>7193754</v>
+        <v>7193823</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,53 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116705152</v>
+        <v>372674</v>
       </c>
       <c r="B5" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödingsjön, Fjällboberg, Ås lm</t>
+          <t>V Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536083</v>
+        <v>536100</v>
       </c>
       <c r="R5" t="n">
-        <v>7193792</v>
+        <v>7193662</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2012-08-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2012-08-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,69 +1077,69 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116705069</v>
+        <v>372676</v>
       </c>
       <c r="B6" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rödingsjön, Fjällboberg, Ås lm</t>
+          <t>V Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536079</v>
+        <v>535997</v>
       </c>
       <c r="R6" t="n">
-        <v>7193823</v>
+        <v>7193626</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,22 +1163,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2012-08-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2012-08-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,31 +1179,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116705107</v>
+        <v>116705166</v>
       </c>
       <c r="B7" t="n">
-        <v>77377</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536071</v>
+        <v>536069</v>
       </c>
       <c r="R7" t="n">
-        <v>7193800</v>
+        <v>7193799</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1357,15 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116705080</v>
+        <v>116705088</v>
       </c>
       <c r="B8" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,39 +1318,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536135</v>
+        <v>535979</v>
       </c>
       <c r="R8" t="n">
-        <v>7193572</v>
+        <v>7193612</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,15 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116705144</v>
+        <v>116705089</v>
       </c>
       <c r="B9" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536087</v>
+        <v>536040</v>
       </c>
       <c r="R9" t="n">
-        <v>7193616</v>
+        <v>7193749</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1484,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1494,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,15 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116705140</v>
+        <v>116705090</v>
       </c>
       <c r="B10" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535979</v>
+        <v>536027</v>
       </c>
       <c r="R10" t="n">
-        <v>7193612</v>
+        <v>7193751</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1591,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1601,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,15 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116705079</v>
+        <v>116705091</v>
       </c>
       <c r="B11" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,39 +1639,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536125</v>
+        <v>536023</v>
       </c>
       <c r="R11" t="n">
-        <v>7193572</v>
+        <v>7193732</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116705146</v>
+        <v>116705092</v>
       </c>
       <c r="B12" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536040</v>
+        <v>536033</v>
       </c>
       <c r="R12" t="n">
-        <v>7193749</v>
+        <v>7193752</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,37 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116705085</v>
+        <v>116705093</v>
       </c>
       <c r="B13" t="n">
-        <v>79550</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535975</v>
+        <v>536043</v>
       </c>
       <c r="R13" t="n">
-        <v>7193612</v>
+        <v>7193764</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,15 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116705083</v>
+        <v>116705071</v>
       </c>
       <c r="B14" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,39 +1960,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536068</v>
+        <v>536026</v>
       </c>
       <c r="R14" t="n">
-        <v>7193608</v>
+        <v>7193800</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,37 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116705138</v>
+        <v>116705072</v>
       </c>
       <c r="B15" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535970</v>
+        <v>536065</v>
       </c>
       <c r="R15" t="n">
-        <v>7193675</v>
+        <v>7193799</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,15 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116705109</v>
+        <v>116705138</v>
       </c>
       <c r="B16" t="n">
-        <v>77781</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2308,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536070</v>
+        <v>535970</v>
       </c>
       <c r="R16" t="n">
-        <v>7193799</v>
+        <v>7193675</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,19 +2270,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116705150</v>
+        <v>116705140</v>
       </c>
       <c r="B17" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2420,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536044</v>
+        <v>535979</v>
       </c>
       <c r="R17" t="n">
-        <v>7193762</v>
+        <v>7193612</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,37 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116705088</v>
+        <v>116705141</v>
       </c>
       <c r="B18" t="n">
-        <v>79522</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535979</v>
+        <v>536069</v>
       </c>
       <c r="R18" t="n">
-        <v>7193612</v>
+        <v>7193606</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,37 +2484,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116705092</v>
+        <v>116705142</v>
       </c>
       <c r="B19" t="n">
-        <v>79522</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2644,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536033</v>
+        <v>536125</v>
       </c>
       <c r="R19" t="n">
-        <v>7193752</v>
+        <v>7193569</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,37 +2591,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>116705090</v>
+        <v>116705143</v>
       </c>
       <c r="B20" t="n">
-        <v>79522</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2756,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536027</v>
+        <v>536136</v>
       </c>
       <c r="R20" t="n">
-        <v>7193751</v>
+        <v>7193569</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,37 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>116705089</v>
+        <v>116705144</v>
       </c>
       <c r="B21" t="n">
-        <v>79522</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2868,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536040</v>
+        <v>536087</v>
       </c>
       <c r="R21" t="n">
-        <v>7193749</v>
+        <v>7193616</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2903,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,37 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116705072</v>
+        <v>116705145</v>
       </c>
       <c r="B22" t="n">
-        <v>91139</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2980,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536065</v>
+        <v>536070</v>
       </c>
       <c r="R22" t="n">
-        <v>7193799</v>
+        <v>7193666</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3015,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,37 +2912,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>116705103</v>
+        <v>116705146</v>
       </c>
       <c r="B23" t="n">
-        <v>79557</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3092,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536044</v>
+        <v>536040</v>
       </c>
       <c r="R23" t="n">
-        <v>7193762</v>
+        <v>7193749</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,37 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116705115</v>
+        <v>116705147</v>
       </c>
       <c r="B24" t="n">
-        <v>90444</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3204,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536038</v>
+        <v>536027</v>
       </c>
       <c r="R24" t="n">
-        <v>7193739</v>
+        <v>7193753</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,19 +3126,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>116705153</v>
+        <v>116705148</v>
       </c>
       <c r="B25" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3316,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536072</v>
+        <v>536032</v>
       </c>
       <c r="R25" t="n">
-        <v>7193803</v>
+        <v>7193744</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3351,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,19 +3233,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116705143</v>
+        <v>116705149</v>
       </c>
       <c r="B26" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3428,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536136</v>
+        <v>536037</v>
       </c>
       <c r="R26" t="n">
-        <v>7193569</v>
+        <v>7193757</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3463,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,19 +3340,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116705147</v>
+        <v>116705150</v>
       </c>
       <c r="B27" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3540,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536027</v>
+        <v>536044</v>
       </c>
       <c r="R27" t="n">
-        <v>7193753</v>
+        <v>7193762</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3575,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3585,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,19 +3447,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116705145</v>
+        <v>116705151</v>
       </c>
       <c r="B28" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3652,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536070</v>
+        <v>536027</v>
       </c>
       <c r="R28" t="n">
-        <v>7193666</v>
+        <v>7193799</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3687,7 +3517,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3697,7 +3527,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3724,19 +3554,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>116705148</v>
+        <v>116705152</v>
       </c>
       <c r="B29" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3764,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536032</v>
+        <v>536083</v>
       </c>
       <c r="R29" t="n">
-        <v>7193744</v>
+        <v>7193792</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3799,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,37 +3661,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>116705100</v>
+        <v>116705153</v>
       </c>
       <c r="B30" t="n">
-        <v>79521</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3876,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536028</v>
+        <v>536072</v>
       </c>
       <c r="R30" t="n">
-        <v>7193750</v>
+        <v>7193803</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3911,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,15 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>116705101</v>
+        <v>116705100</v>
       </c>
       <c r="B31" t="n">
-        <v>79521</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536022</v>
+        <v>536028</v>
       </c>
       <c r="R31" t="n">
-        <v>7193732</v>
+        <v>7193750</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4023,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,15 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>116705149</v>
+        <v>116705101</v>
       </c>
       <c r="B32" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536037</v>
+        <v>536022</v>
       </c>
       <c r="R32" t="n">
-        <v>7193757</v>
+        <v>7193732</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4135,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,37 +3982,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>116705141</v>
+        <v>116705085</v>
       </c>
       <c r="B33" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4212,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536069</v>
+        <v>535975</v>
       </c>
       <c r="R33" t="n">
-        <v>7193606</v>
+        <v>7193612</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4247,7 +4052,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4062,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,37 +4089,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>116705093</v>
+        <v>116705086</v>
       </c>
       <c r="B34" t="n">
-        <v>79522</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4324,10 +4124,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536043</v>
+        <v>536034</v>
       </c>
       <c r="R34" t="n">
-        <v>7193764</v>
+        <v>7193754</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4359,7 +4159,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4369,7 +4169,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4396,37 +4196,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>116705091</v>
+        <v>116705169</v>
       </c>
       <c r="B35" t="n">
-        <v>79522</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4436,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536023</v>
+        <v>536034</v>
       </c>
       <c r="R35" t="n">
-        <v>7193732</v>
+        <v>7193754</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4471,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4481,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4508,37 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>116705166</v>
+        <v>116705103</v>
       </c>
       <c r="B36" t="n">
-        <v>82217</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4548,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536069</v>
+        <v>536044</v>
       </c>
       <c r="R36" t="n">
-        <v>7193799</v>
+        <v>7193762</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4583,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4620,15 +4410,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>116705142</v>
+        <v>116705079</v>
       </c>
       <c r="B37" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4636,24 +4421,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
@@ -4663,7 +4453,7 @@
         <v>536125</v>
       </c>
       <c r="R37" t="n">
-        <v>7193569</v>
+        <v>7193572</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4732,50 +4522,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>116705086</v>
+        <v>116705080</v>
       </c>
       <c r="B38" t="n">
-        <v>79550</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536034</v>
+        <v>536135</v>
       </c>
       <c r="R38" t="n">
-        <v>7193754</v>
+        <v>7193572</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4807,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4817,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,6 +4631,225 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>116705083</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Rödingsjön, Fjällboberg, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>536068</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7193608</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>116705107</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Rödingsjön, Fjällboberg, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>536071</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7193800</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
